--- a/React_Notes.xlsx
+++ b/React_Notes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\learning\React\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E20A752-4529-4FCE-995A-ED7A4E6DC9C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7096D0B-1ED4-4E50-8AEC-26D347E2EF08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="864" activeTab="3" xr2:uid="{87C7C703-CD04-4003-9495-A8F0A927737C}"/>
   </bookViews>
@@ -26,6 +26,7 @@
     <sheet name="状态管理" sheetId="10" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -49,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="249">
   <si>
     <t>获取对象属性名集合</t>
   </si>
@@ -2033,12 +2034,27 @@
       <t>(本项目当前使用的框架)</t>
     </r>
   </si>
+  <si>
+    <t>React Native 跳转方式</t>
+  </si>
+  <si>
+    <t>在 React Navigation 体系中，页面跳转不是一种，而是三种形态的组合：</t>
+  </si>
+  <si>
+    <t xml:space="preserve">               ┌── 1. Stack (堆栈导航)  ──&gt; 像叠盘子一样：从右向左推入新页面，右滑返回上一层</t>
+  </si>
+  <si>
+    <t xml:space="preserve">               └── 3. Drawer (抽屉导航) ──&gt; 侧边滑出菜单栏（如网易云音乐、Twitter 侧边栏）</t>
+  </si>
+  <si>
+    <t>App 总导航容器   ├── 2. Tab (底栏导航)    ──&gt; 像微信底栏：首页、通讯录、发现、我，平级瞬间切换</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2152,6 +2168,12 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9.9"/>
+      <color rgb="FF202020"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -2209,7 +2231,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2263,7 +2285,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2278,6 +2300,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3963,7 +3994,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="27" spans="1:1" ht="72.5">
+    <row r="27" spans="1:1" ht="87">
       <c r="A27" s="26" t="s">
         <v>217</v>
       </c>
@@ -4050,7 +4081,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{121629D7-1E17-4996-97ED-59EBDF426801}">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="22.36328125" customWidth="1"/>
@@ -4306,6 +4337,31 @@
       </c>
       <c r="D24" s="23" t="s">
         <v>242</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="16">
+      <c r="A27" s="27" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="16">
+      <c r="A28" s="29" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="28" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="28" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="28" t="s">
+        <v>247</v>
       </c>
     </row>
   </sheetData>

--- a/React_Notes.xlsx
+++ b/React_Notes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\learning\React\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7096D0B-1ED4-4E50-8AEC-26D347E2EF08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66FEBE64-5B68-4BE9-8100-CC1C7EF98F95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="864" activeTab="3" xr2:uid="{87C7C703-CD04-4003-9495-A8F0A927737C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="864" activeTab="10" xr2:uid="{87C7C703-CD04-4003-9495-A8F0A927737C}"/>
   </bookViews>
   <sheets>
     <sheet name="TS" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="278">
   <si>
     <t>获取对象属性名集合</t>
   </si>
@@ -2048,6 +2048,96 @@
   </si>
   <si>
     <t>App 总导航容器   ├── 2. Tab (底栏导航)    ──&gt; 像微信底栏：首页、通讯录、发现、我，平级瞬间切换</t>
+  </si>
+  <si>
+    <t>状态管理库</t>
+  </si>
+  <si>
+    <t>体积 / 复杂度</t>
+  </si>
+  <si>
+    <t>学习成本</t>
+  </si>
+  <si>
+    <t>核心优势</t>
+  </si>
+  <si>
+    <t>缺点</t>
+  </si>
+  <si>
+    <t>适用场景</t>
+  </si>
+  <si>
+    <t>5 分钟上手</t>
+  </si>
+  <si>
+    <t>极大型团队严格要求单一中心化流向时规范稍弱</t>
+  </si>
+  <si>
+    <t>90% 的新老 React Native / Expo 项目</t>
+  </si>
+  <si>
+    <t>中等</t>
+  </si>
+  <si>
+    <t>不适合管理纯前端 UI 状态（如弹窗开关、购物车本地选中）</t>
+  </si>
+  <si>
+    <t>网络请求密集、需要复杂数据缓存的应用</t>
+  </si>
+  <si>
+    <t>极低</t>
+  </si>
+  <si>
+    <t>较高</t>
+  </si>
+  <si>
+    <t>模板代码多、心智负担重，对中小项目属于“大炮打蚊子”</t>
+  </si>
+  <si>
+    <t>状态更新时容易引起整棵子树不必要的重复渲染，数据复杂时容易嵌套地狱</t>
+  </si>
+  <si>
+    <t>极简单的状态（如当前的深浅色主题、当前语言）</t>
+  </si>
+  <si>
+    <t>历史遗留项目、数百人协作的超大型政企 App</t>
+  </si>
+  <si>
+    <t>Zustand (当前首选推荐)</t>
+  </si>
+  <si>
+    <t>极小 (~1KB)极低</t>
+  </si>
+  <si>
+    <t>TanStack Query(React Query)</t>
+  </si>
+  <si>
+    <t>• 专为 API 异步数据 设计• 自动处理加载中、错误、接口缓存、失效刷新、下拉静默更新</t>
+  </si>
+  <si>
+    <t>Context API(React 自带)</t>
+  </si>
+  <si>
+    <t>0 KB(内置)</t>
+  </si>
+  <si>
+    <t>• 无需安装任何第三方库• 与 React 结合最自然</t>
+  </si>
+  <si>
+    <t>Redux Toolkit(RTK)</t>
+  </si>
+  <si>
+    <t>偏大较繁琐</t>
+  </si>
+  <si>
+    <t>• 老牌企业级标准，规范极其严苛• Time-travel 时间旅行调试工具完善</t>
+  </si>
+  <si>
+    <t>• 没有 Redux 繁琐的 Action/Reducer
+• 基于纯 Hook 消费，精准更新不卡顿
+• 可在 React 组件外直接读写状态（例如直接在 Axios 拦截器里读 Token！）
+• 原生支持持久化插件（自动存入本地存储）</t>
   </si>
 </sst>
 </file>
@@ -2231,7 +2321,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2309,6 +2399,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3721,7 +3814,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C4C7C03-E584-4184-AE80-7A093EB5F18C}">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultColWidth="15.7265625" defaultRowHeight="19" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="22.90625" customWidth="1"/>
@@ -3731,9 +3824,16 @@
     <col min="5" max="5" width="17.6328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28.453125" customWidth="1"/>
     <col min="7" max="7" width="42.08984375" customWidth="1"/>
+    <col min="8" max="8" width="5.1796875" customWidth="1"/>
+    <col min="9" max="9" width="28.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="49.54296875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="29.54296875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="25.08984375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19" customHeight="1" thickBot="1">
+    <row r="1" spans="1:14" ht="19" customHeight="1" thickBot="1">
       <c r="A1" s="18" t="s">
         <v>153</v>
       </c>
@@ -3752,8 +3852,26 @@
       <c r="G1" s="14" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="28.5" thickBot="1">
+      <c r="I1" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="J1" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="K1" s="30" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="M1" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="N1" s="30" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="73" thickBot="1">
       <c r="A2" s="19" t="s">
         <v>156</v>
       </c>
@@ -3772,8 +3890,26 @@
       <c r="G2" s="16" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="15" thickBot="1">
+      <c r="I2" s="30" t="s">
+        <v>267</v>
+      </c>
+      <c r="J2" s="30" t="s">
+        <v>268</v>
+      </c>
+      <c r="K2" s="30" t="s">
+        <v>255</v>
+      </c>
+      <c r="L2" s="30" t="s">
+        <v>277</v>
+      </c>
+      <c r="M2" s="30" t="s">
+        <v>256</v>
+      </c>
+      <c r="N2" s="30" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="44" thickBot="1">
       <c r="A3" s="19" t="s">
         <v>158</v>
       </c>
@@ -3792,8 +3928,26 @@
       <c r="G3" s="16" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1">
+      <c r="I3" s="30" t="s">
+        <v>269</v>
+      </c>
+      <c r="J3" s="30" t="s">
+        <v>258</v>
+      </c>
+      <c r="K3" s="30" t="s">
+        <v>258</v>
+      </c>
+      <c r="L3" s="30" t="s">
+        <v>270</v>
+      </c>
+      <c r="M3" s="30" t="s">
+        <v>259</v>
+      </c>
+      <c r="N3" s="30" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="44" thickBot="1">
       <c r="A4" s="19" t="s">
         <v>159</v>
       </c>
@@ -3812,8 +3966,26 @@
       <c r="G4" s="16" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="78.5" thickBot="1">
+      <c r="I4" s="30" t="s">
+        <v>271</v>
+      </c>
+      <c r="J4" s="30" t="s">
+        <v>272</v>
+      </c>
+      <c r="K4" s="30" t="s">
+        <v>261</v>
+      </c>
+      <c r="L4" s="30" t="s">
+        <v>273</v>
+      </c>
+      <c r="M4" s="30" t="s">
+        <v>264</v>
+      </c>
+      <c r="N4" s="30" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="78.5" thickBot="1">
       <c r="A5" s="19" t="s">
         <v>162</v>
       </c>
@@ -3832,8 +4004,26 @@
       <c r="G5" s="17" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="14.5">
+      <c r="I5" s="30" t="s">
+        <v>274</v>
+      </c>
+      <c r="J5" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="K5" s="30" t="s">
+        <v>262</v>
+      </c>
+      <c r="L5" s="30" t="s">
+        <v>276</v>
+      </c>
+      <c r="M5" s="30" t="s">
+        <v>263</v>
+      </c>
+      <c r="N5" s="30" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="14.5">
       <c r="A6" s="19" t="s">
         <v>165</v>
       </c>
@@ -3844,7 +4034,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="29">
+    <row r="7" spans="1:14" ht="29">
       <c r="A7" s="19" t="s">
         <v>168</v>
       </c>
@@ -3855,11 +4045,11 @@
         <v>170</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="35" customHeight="1"/>
-    <row r="9" spans="1:7" ht="34.5" customHeight="1"/>
-    <row r="10" spans="1:7" ht="34.5" customHeight="1"/>
-    <row r="11" spans="1:7" ht="34.5" customHeight="1"/>
-    <row r="12" spans="1:7" ht="74.5" customHeight="1"/>
+    <row r="8" spans="1:14" ht="35" customHeight="1"/>
+    <row r="9" spans="1:14" ht="34.5" customHeight="1"/>
+    <row r="10" spans="1:14" ht="34.5" customHeight="1"/>
+    <row r="11" spans="1:14" ht="34.5" customHeight="1"/>
+    <row r="12" spans="1:14" ht="74.5" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/React_Notes.xlsx
+++ b/React_Notes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\learning\React\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66FEBE64-5B68-4BE9-8100-CC1C7EF98F95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CC522AD-9FF3-4A92-8D42-0A65B8017C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="864" activeTab="10" xr2:uid="{87C7C703-CD04-4003-9495-A8F0A927737C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="864" activeTab="3" xr2:uid="{87C7C703-CD04-4003-9495-A8F0A927737C}"/>
   </bookViews>
   <sheets>
     <sheet name="TS" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,6 @@
     <sheet name="状态管理" sheetId="10" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -50,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="279">
   <si>
     <t>获取对象属性名集合</t>
   </si>
@@ -1148,61 +1147,6 @@
   </si>
   <si>
     <r>
-      <t>&lt;TouchableOpacity&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Google Sans Text"/>
-        <family val="2"/>
-      </rPr>
-      <t>&lt;Pressable&gt;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>点击交互组件</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">。RN 没有原生的 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Google Sans Text"/>
-        <family val="2"/>
-      </rPr>
-      <t>&lt;button&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 标签，通常用这两者来包裹自定义的点击区域。</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>&lt;ul&gt;</t>
     </r>
     <r>
@@ -1786,49 +1730,6 @@
     <t>MUI (Material-UI)</t>
   </si>
   <si>
-    <r>
-      <t>🌟 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="7"/>
-        <color rgb="FF202020"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>目前最成熟稳定、开箱即用首选</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <color rgb="FF202020"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>&lt;br&gt;• Google MD3 设计规范官方实现&lt;br&gt;• 拥有极其完整的组件库（卡片、弹窗、输入框、底栏）&lt;br&gt;• 内置深色/浅色模式切换、高保真阴影与无障碍支持&lt;br&gt;• </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="7"/>
-        <color rgb="FF202020"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>零配置</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <color rgb="FF202020"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>，与 Expo 和 React 19 兼容性极佳</t>
-    </r>
-  </si>
-  <si>
     <t>2. NativeWind</t>
   </si>
   <si>
@@ -1838,48 +1739,6 @@
     <t>Tailwind CSS</t>
   </si>
   <si>
-    <r>
-      <t>🔥 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="7"/>
-        <color rgb="FF202020"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>近两年海外最火爆</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <color rgb="FF202020"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>&lt;br&gt;• 允许你在 React Native 里写原子类：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.9"/>
-        <color rgb="FF606060"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t>className="flex-1 bg-blue-500 p-4 rounded-xl"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <color rgb="FF202020"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>&lt;br&gt;• 极适合熟悉 Web 端 Tailwind 的开发者</t>
-    </r>
-  </si>
-  <si>
     <t>3. Tamagui</t>
   </si>
   <si>
@@ -1889,30 +1748,6 @@
     <t>Stitches / Radix</t>
   </si>
   <si>
-    <r>
-      <t>⚡ </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="7"/>
-        <color rgb="FF202020"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>极客与性能首选</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <color rgb="FF202020"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>&lt;br&gt;• 编译期优化：把样式直接编译成原生，几乎 0 运行时开销&lt;br&gt;• 同一套代码可在 Web 和手机上同时完美运行（真正的跨全端）</t>
-    </r>
-  </si>
-  <si>
     <t>4. Ant Design Mobile RN</t>
   </si>
   <si>
@@ -1920,30 +1755,6 @@
   </si>
   <si>
     <t>Ant Design</t>
-  </si>
-  <si>
-    <r>
-      <t>🇨🇳 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="7"/>
-        <color rgb="FF202020"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>国内企业与金融项目常见</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <color rgb="FF202020"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>&lt;br&gt;• 阿里巴巴出品，Ant Design 的移动端 RN 版本&lt;br&gt;• 适合做国内政企、OA、后台协同类 App</t>
-    </r>
   </si>
   <si>
     <r>
@@ -1977,30 +1788,6 @@
   </si>
   <si>
     <r>
-      <t>🛠️ </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="7"/>
-        <color rgb="FF202020"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>设计自由度高</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <color rgb="FF202020"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>&lt;br&gt;• 前身是老牌框架 NativeBase（后因性能重构成 Gluestack）&lt;br&gt;• 采用类似 shadcn/ui 的设计理念，支持高度定制与复制源码</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -2122,29 +1909,170 @@
     <t>0 KB(内置)</t>
   </si>
   <si>
-    <t>• 无需安装任何第三方库• 与 React 结合最自然</t>
-  </si>
-  <si>
     <t>Redux Toolkit(RTK)</t>
   </si>
   <si>
     <t>偏大较繁琐</t>
-  </si>
-  <si>
-    <t>• 老牌企业级标准，规范极其严苛• Time-travel 时间旅行调试工具完善</t>
   </si>
   <si>
     <t>• 没有 Redux 繁琐的 Action/Reducer
 • 基于纯 Hook 消费，精准更新不卡顿
 • 可在 React 组件外直接读写状态（例如直接在 Axios 拦截器里读 Token！）
 • 原生支持持久化插件（自动存入本地存储）</t>
+  </si>
+  <si>
+    <t>• 无需安装任何第三方库
+• 与 React 结合最自然</t>
+  </si>
+  <si>
+    <t>• 老牌企业级标准，规范极其严苛
+• Time-travel 时间旅行调试工具完善</t>
+  </si>
+  <si>
+    <r>
+      <t>🌟 目前最成熟稳定、开箱即用首选</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;br&gt;• Google MD3 设计规范官方实现&lt;br&gt;• 拥有极其完整的组件库（卡片、弹窗、输入框、底栏）&lt;br&gt;• 内置深色/浅色模式切换、高保真阴影与无障碍支持&lt;br&gt;• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>零配置</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>，与 Expo 和 React 19 兼容性极佳</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>🔥 近两年海外最火爆</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;br&gt;• 允许你在 React Native 里写原子类：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF606060"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>className="flex-1 bg-blue-500 p-4 rounded-xl"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;br&gt;• 极适合熟悉 Web 端 Tailwind 的开发者</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>⚡ 极客与性能首选</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;br&gt;• 编译期优化：把样式直接编译成原生，几乎 0 运行时开销&lt;br&gt;• 同一套代码可在 Web 和手机上同时完美运行（真正的跨全端）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>🇨🇳 国内企业与金融项目常见</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;br&gt;• 阿里巴巴出品，Ant Design 的移动端 RN 版本&lt;br&gt;• 适合做国内政企、OA、后台协同类 App</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>🛠️ 设计自由度高</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;br&gt;• 前身是老牌框架 NativeBase（后因性能重构成 Gluestack）&lt;br&gt;• 采用类似 shadcn/ui 的设计理念，支持高度定制与复制源码</t>
+    </r>
+  </si>
+  <si>
+    <t>mock:json-server / Mock Service Worker</t>
+  </si>
+  <si>
+    <t>&lt;Button&gt;	React Native 内置按钮组件，提供基础按钮功能，但样式自定义能力有限。
+&lt;Pressable&gt;	通用点击交互组件，可以包裹自定义 UI，支持按压状态和样式控制。
+&lt;TouchableOpacity&gt;	点击交互组件，点击时通过透明度变化提供反馈。</t>
+  </si>
+  <si>
+    <r>
+      <t>&lt;Button&gt;
+&lt;TouchableOpacity&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>&lt;Pressable&gt;</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2189,13 +2117,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Google Sans Text"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="7"/>
-      <color rgb="FF202020"/>
-      <name val="Segoe UI"/>
       <family val="2"/>
     </font>
     <font>
@@ -2245,12 +2166,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="9.9"/>
-      <color rgb="FF606060"/>
-      <name val="Courier New"/>
-      <family val="3"/>
-    </font>
-    <font>
       <b/>
       <u/>
       <sz val="10"/>
@@ -2264,8 +2179,27 @@
       <name val="Courier New"/>
       <family val="3"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF202020"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF202020"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF606060"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2275,6 +2209,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2321,7 +2261,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2378,30 +2318,39 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3825,8 +3774,8 @@
     <col min="6" max="6" width="28.453125" customWidth="1"/>
     <col min="7" max="7" width="42.08984375" customWidth="1"/>
     <col min="8" max="8" width="5.1796875" customWidth="1"/>
-    <col min="9" max="9" width="28.08984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7265625" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.26953125" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="49.54296875" style="2" customWidth="1"/>
     <col min="13" max="13" width="29.54296875" style="2" customWidth="1"/>
@@ -3853,22 +3802,22 @@
         <v>141</v>
       </c>
       <c r="I1" s="30" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="J1" s="30" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="K1" s="30" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="L1" s="30" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="M1" s="30" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="N1" s="30" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="73" thickBot="1">
@@ -3891,22 +3840,22 @@
         <v>143</v>
       </c>
       <c r="I2" s="30" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="J2" s="30" t="s">
+        <v>261</v>
+      </c>
+      <c r="K2" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="L2" s="30" t="s">
         <v>268</v>
       </c>
-      <c r="K2" s="30" t="s">
-        <v>255</v>
-      </c>
-      <c r="L2" s="30" t="s">
-        <v>277</v>
-      </c>
       <c r="M2" s="30" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="N2" s="30" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="44" thickBot="1">
@@ -3929,22 +3878,22 @@
         <v>146</v>
       </c>
       <c r="I3" s="30" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="J3" s="30" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="K3" s="30" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="L3" s="30" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="M3" s="30" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="N3" s="30" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="44" thickBot="1">
@@ -3967,22 +3916,22 @@
         <v>149</v>
       </c>
       <c r="I4" s="30" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="J4" s="30" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="K4" s="30" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="L4" s="30" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="M4" s="30" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="N4" s="30" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="78.5" thickBot="1">
@@ -4005,22 +3954,22 @@
         <v>151</v>
       </c>
       <c r="I5" s="30" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="J5" s="30" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="K5" s="30" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="L5" s="30" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="M5" s="30" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="N5" s="30" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="14.5">
@@ -4125,6 +4074,9 @@
       <c r="A7" t="s">
         <v>68</v>
       </c>
+      <c r="C7" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
@@ -4181,12 +4133,12 @@
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" ht="87">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" ht="72.5">
       <c r="A27" s="26" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -4277,7 +4229,7 @@
     <col min="1" max="1" width="22.36328125" customWidth="1"/>
     <col min="2" max="2" width="24.26953125" customWidth="1"/>
     <col min="3" max="3" width="47.7265625" customWidth="1"/>
-    <col min="4" max="4" width="43.1796875" customWidth="1"/>
+    <col min="4" max="4" width="50.7265625" customWidth="1"/>
     <col min="5" max="8" width="12.26953125" style="22" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4292,73 +4244,73 @@
         <v>175</v>
       </c>
       <c r="D1" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="85" customHeight="1" thickBot="1">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="28.5" thickBot="1">
       <c r="A2" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="31" t="s">
         <v>177</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="49" customHeight="1" thickBot="1">
+    <row r="3" spans="1:4" ht="42.5" thickBot="1">
       <c r="A3" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="31" t="s">
         <v>180</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="49" customHeight="1" thickBot="1">
+    <row r="4" spans="1:4" ht="42.5" thickBot="1">
       <c r="A4" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="31" t="s">
         <v>183</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="49" customHeight="1" thickBot="1">
+    <row r="5" spans="1:4" ht="15" thickBot="1">
       <c r="A5" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="31" t="s">
         <v>186</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="49" customHeight="1" thickBot="1">
+    <row r="6" spans="1:4" ht="98.5" thickBot="1">
       <c r="A6" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="31" t="s">
+        <v>278</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="28.5" thickBot="1">
+      <c r="A7" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="B7" s="31" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="49" customHeight="1" thickBot="1">
-      <c r="A7" s="17" t="s">
+      <c r="C7" s="14" t="s">
         <v>191</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>192</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="16">
@@ -4366,192 +4318,192 @@
         <v>139</v>
       </c>
       <c r="B11" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="D11" s="23" t="s">
         <v>194</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="D11" s="23" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="32">
       <c r="A12" s="23" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B12" s="24" t="s">
+        <v>202</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>203</v>
+      </c>
+      <c r="D12" s="23" t="s">
         <v>204</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="D12" s="23" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="25" customHeight="1">
       <c r="A13" s="23" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="48">
       <c r="A14" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="38.5" customHeight="1">
       <c r="A15" s="23" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B15" s="25" t="s">
+        <v>209</v>
+      </c>
+      <c r="C15" s="23" t="s">
+        <v>210</v>
+      </c>
+      <c r="D15" s="24" t="s">
         <v>211</v>
-      </c>
-      <c r="C15" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="D15" s="24" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="32">
       <c r="A16" s="23" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B16" s="25" t="s">
+        <v>212</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="D16" s="24" t="s">
         <v>214</v>
-      </c>
-      <c r="C16" s="25" t="s">
-        <v>215</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="16">
       <c r="A19" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="C19" s="23" t="s">
         <v>220</v>
       </c>
-      <c r="B19" s="23" t="s">
+      <c r="D19" s="23" t="s">
         <v>221</v>
       </c>
-      <c r="C19" s="23" t="s">
+    </row>
+    <row r="20" spans="1:4" ht="105">
+      <c r="A20" s="32" t="s">
+        <v>236</v>
+      </c>
+      <c r="B20" s="24" t="s">
         <v>222</v>
       </c>
-      <c r="D19" s="23" t="s">
+      <c r="C20" s="24" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" ht="58">
-      <c r="A20" s="23" t="s">
-        <v>243</v>
-      </c>
-      <c r="B20" s="24" t="s">
+      <c r="D20" s="33" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="70">
+      <c r="A21" s="23" t="s">
         <v>224</v>
       </c>
-      <c r="C20" s="24" t="s">
+      <c r="B21" s="23" t="s">
         <v>225</v>
       </c>
-      <c r="D20" s="23" t="s">
+      <c r="C21" s="23" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" ht="42">
-      <c r="A21" s="23" t="s">
+      <c r="D21" s="33" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="70">
+      <c r="A22" s="23" t="s">
         <v>227</v>
       </c>
-      <c r="B21" s="23" t="s">
+      <c r="B22" s="24" t="s">
         <v>228</v>
       </c>
-      <c r="C21" s="23" t="s">
+      <c r="C22" s="24" t="s">
         <v>229</v>
       </c>
-      <c r="D21" s="23" t="s">
+      <c r="D22" s="33" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="70">
+      <c r="A23" s="23" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" ht="37">
-      <c r="A22" s="23" t="s">
+      <c r="B23" s="23" t="s">
         <v>231</v>
       </c>
-      <c r="B22" s="24" t="s">
+      <c r="C23" s="23" t="s">
         <v>232</v>
       </c>
-      <c r="C22" s="24" t="s">
+      <c r="D23" s="33" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="70">
+      <c r="A24" s="23" t="s">
         <v>233</v>
       </c>
-      <c r="D22" s="23" t="s">
+      <c r="B24" s="24" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" ht="32">
-      <c r="A23" s="23" t="s">
+      <c r="C24" s="24" t="s">
         <v>235</v>
       </c>
-      <c r="B23" s="23" t="s">
-        <v>236</v>
-      </c>
-      <c r="C23" s="23" t="s">
-        <v>237</v>
-      </c>
-      <c r="D23" s="23" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="37">
-      <c r="A24" s="23" t="s">
-        <v>239</v>
-      </c>
-      <c r="B24" s="24" t="s">
-        <v>240</v>
-      </c>
-      <c r="C24" s="24" t="s">
-        <v>241</v>
-      </c>
-      <c r="D24" s="23" t="s">
-        <v>242</v>
+      <c r="D24" s="33" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="16">
       <c r="A27" s="27" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="16">
       <c r="A28" s="29" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="28" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="28" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="28" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
